--- a/logs/LINERNAtemplate.xlsx
+++ b/logs/LINERNAtemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mikej10\advbfx\LINEs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikej\Documents\Career\Georges\Ule\intron_retention_propensity\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093628B8-10EA-4981-A437-93BC98B32984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B00A12-F7EB-48D9-ACFC-1D043A05DA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -592,12 +592,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -905,38 +908,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="62.109375" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" customWidth="1"/>
-    <col min="12" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="21.6640625" customWidth="1"/>
-    <col min="16" max="17" width="14.6640625" customWidth="1"/>
-    <col min="18" max="18" width="51.6640625" customWidth="1"/>
-    <col min="19" max="19" width="21.6640625" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" customWidth="1"/>
-    <col min="21" max="24" width="11.6640625" customWidth="1"/>
-    <col min="25" max="25" width="15.6640625" customWidth="1"/>
-    <col min="26" max="26" width="11.6640625" customWidth="1"/>
-    <col min="27" max="27" width="30.6640625" customWidth="1"/>
-    <col min="28" max="28" width="13.6640625" customWidth="1"/>
-    <col min="29" max="29" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="62.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="13" width="20.7109375" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="15" max="15" width="21.7109375" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" customWidth="1"/>
+    <col min="18" max="18" width="51.7109375" customWidth="1"/>
+    <col min="19" max="19" width="21.7109375" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" customWidth="1"/>
+    <col min="21" max="24" width="11.7109375" customWidth="1"/>
+    <col min="25" max="25" width="15.7109375" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" customWidth="1"/>
+    <col min="27" max="27" width="30.7109375" customWidth="1"/>
+    <col min="28" max="28" width="13.7109375" customWidth="1"/>
+    <col min="29" max="29" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -951,7 +954,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1021,7 +1024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -1071,7 +1074,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1121,7 +1124,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1171,7 +1174,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -1271,7 +1274,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1321,7 +1324,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -1421,7 +1424,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -1521,7 +1524,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -1571,7 +1574,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -1671,7 +1674,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -1721,7 +1724,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -1821,7 +1824,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -1871,7 +1874,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -1971,7 +1974,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>88</v>
       </c>
@@ -2071,7 +2074,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -2121,7 +2124,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>90</v>
       </c>
@@ -2171,7 +2174,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -2221,7 +2224,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -2271,7 +2274,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -2321,7 +2324,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2371,7 +2374,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -2421,7 +2424,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>96</v>
       </c>
@@ -2471,7 +2474,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -2521,7 +2524,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>98</v>
       </c>
@@ -2571,7 +2574,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>99</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>100</v>
       </c>
@@ -2671,7 +2674,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>102</v>
       </c>
@@ -2771,7 +2774,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>103</v>
       </c>
